--- a/data/dividends_info_20260815.xlsx
+++ b/data/dividends_info_20260815.xlsx
@@ -710,8 +710,12 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>46.65499877929688</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1929053742467087</v>
+      </c>
       <c r="J6" t="n">
         <v>121</v>
       </c>
@@ -1176,8 +1180,12 @@
           <t>IT0003132476</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>23.69499969482422</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.139480917819877</v>
+      </c>
       <c r="J16" t="n">
         <v>37</v>
       </c>
@@ -1266,8 +1274,12 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>46.65499877929688</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1929053742467087</v>
+      </c>
       <c r="J18" t="n">
         <v>37</v>
       </c>
@@ -1497,8 +1509,12 @@
           <t>IT0005187460</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>4.96999979019165</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7645875574279384</v>
+      </c>
       <c r="J23" t="n">
         <v>-12</v>
       </c>
@@ -3153,163 +3169,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sesa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>